--- a/priv/norm_templates/FA1-norm.xlsx
+++ b/priv/norm_templates/FA1-norm.xlsx
@@ -165,7 +165,7 @@
     <t>PRIVACY NOTICE: this form contains personal data, please check FIDE Privacy policy at www.fide.com/privacy</t>
   </si>
   <si>
-    <t>IA/IO/FT CORNET, Luc (205494)</t>
+    <t>IA/IO CORNET, Luc (205494)</t>
   </si>
 </sst>
 </file>

--- a/priv/norm_templates/FA1-norm.xlsx
+++ b/priv/norm_templates/FA1-norm.xlsx
@@ -165,13 +165,16 @@
     <t>PRIVACY NOTICE: this form contains personal data, please check FIDE Privacy policy at www.fide.com/privacy</t>
   </si>
   <si>
-    <t>IA/IO CORNET, Luc (205494)</t>
+    <t>IA CORNET, Luc (205494)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -375,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -513,6 +516,7 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -932,13 +936,13 @@
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="65"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="65"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1018,7 +1022,7 @@
       <c r="A22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="11"/>
+      <c r="B22" s="65"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
@@ -1046,7 +1050,7 @@
       <c r="A26" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="11"/>
+      <c r="B26" s="65"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/priv/norm_templates/FA1-norm.xlsx
+++ b/priv/norm_templates/FA1-norm.xlsx
@@ -175,7 +175,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -228,6 +228,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -378,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -517,6 +523,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1203,7 +1212,7 @@
         <f>IF(ISBLANK(Invulformulier!$B$6),"",Invulformulier!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="54" t="str">
+      <c r="E9" s="66" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$7),"",Invulformulier!$B$7)</f>
         <v/>
       </c>

--- a/priv/norm_templates/FA1-norm.xlsx
+++ b/priv/norm_templates/FA1-norm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Lucdata\schaken\excel\schaken_2021_2022\fide_ecu\formulieren\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aurora/Downloads/brugesmasterscheck/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899283DF-4F0C-49E8-89AB-A0AB6E409A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DD0C9A-DAB3-9842-B5F3-66C465B39182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invulformulier" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>Federation</t>
   </si>
@@ -129,18 +129,6 @@
     <t>Belgian FIDE Delegate</t>
   </si>
   <si>
-    <t>Recommendation: (please tick the appropriate box).</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The Arbiter's performance was of the required standard for a FIDE Arbiter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The Arbiter still needs to gain more experience.</t>
-  </si>
-  <si>
     <t>the opinion of the Chief Arbiter has qualified for a FIDE Arbiter norm and who requests</t>
   </si>
   <si>
@@ -163,6 +151,9 @@
   </si>
   <si>
     <t>PRIVACY NOTICE: this form contains personal data, please check FIDE Privacy policy at www.fide.com/privacy</t>
+  </si>
+  <si>
+    <t>I hereby confirm that the Arbiter’s performance was of the required standard for a FIDE Arbiter.</t>
   </si>
   <si>
     <t>IA CORNET, Luc (205494)</t>
@@ -172,10 +163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -220,20 +208,8 @@
       <family val="2"/>
     </font>
     <font>
-      <strike/>
-      <sz val="13"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -264,7 +240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -365,26 +341,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -392,13 +353,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -407,7 +368,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -434,7 +394,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -446,28 +406,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -486,33 +466,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -520,15 +473,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -544,9 +493,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -584,9 +533,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -619,26 +568,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -671,26 +603,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -868,15 +783,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="49.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -885,7 +800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -894,7 +809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -903,7 +818,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -912,7 +827,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -923,8 +838,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="12"/>
@@ -932,7 +847,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -941,125 +856,125 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="65"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="65"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="12"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="12"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="10"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="10"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="10"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="10"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="10"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="12"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18" s="26" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="13"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A19" s="26" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="13"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="13"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A21" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="65"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
-        <v>42</v>
+      <c r="B22" s="11"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A23" s="26" t="s">
+        <v>38</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A24" s="26" t="s">
+        <v>37</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A25" s="26" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="11"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="65"/>
+      <c r="B26" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -1080,36 +995,36 @@
   <sheetPr codeName="Blad1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.5" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" customWidth="1"/>
-    <col min="7" max="7" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.5" customWidth="1"/>
     <col min="8" max="9" width="7.6640625" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" customWidth="1"/>
+    <col min="10" max="10" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24.6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="4"/>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="33" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="str">
+      <c r="J2" s="33"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A4" s="38" t="str">
         <f>Invulformulier!A1</f>
         <v>Last Name</v>
       </c>
@@ -1117,7 +1032,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="14"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="42" t="str">
+      <c r="F4" s="38" t="str">
         <f>Invulformulier!A2</f>
         <v>First Name</v>
       </c>
@@ -1126,26 +1041,26 @@
       <c r="I4" s="14"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="str">
+    <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$1),"",Invulformulier!$B$1)</f>
         <v/>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="53" t="str">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$2),"",Invulformulier!$B$2)</f>
         <v/>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="str">
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="48"/>
+    </row>
+    <row r="6" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="38" t="str">
         <f>Invulformulier!A3</f>
         <v>FIDE ID Number</v>
       </c>
@@ -1153,7 +1068,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="14"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="42" t="str">
+      <c r="F6" s="38" t="str">
         <f>Invulformulier!A4</f>
         <v>Federation</v>
       </c>
@@ -1162,32 +1077,32 @@
       <c r="I6" s="14"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="53" t="str">
+    <row r="7" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$3),"",Invulformulier!$B$3)</f>
         <v/>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="53" t="str">
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$4),"",Invulformulier!$B$4)</f>
         <v/>
       </c>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48"/>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="str">
         <f>Invulformulier!A5</f>
         <v>Federation of event</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="26" t="str">
+      <c r="D8" s="25" t="str">
         <f>Invulformulier!A6</f>
         <v>Code of event</v>
       </c>
@@ -1201,34 +1116,34 @@
       <c r="I8" s="2"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="56" t="str">
+    <row r="9" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="49" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$5),"",Invulformulier!$B$5)</f>
         <v>BEL</v>
       </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="28" t="str">
+      <c r="B9" s="50"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="27" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$6),"",Invulformulier!$B$6)</f>
         <v/>
       </c>
-      <c r="E9" s="66" t="str">
+      <c r="E9" s="47" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$7),"",Invulformulier!$B$7)</f>
         <v/>
       </c>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="55"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="str">
         <f>Invulformulier!A8</f>
         <v>Startdate</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="44" t="str">
+      <c r="C10" s="40" t="str">
         <f>Invulformulier!A9</f>
         <v>Enddate</v>
       </c>
@@ -1241,39 +1156,39 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
-      <c r="J10" s="45"/>
-    </row>
-    <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="56" t="str">
+      <c r="J10" s="41"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="49" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$8),"",Invulformulier!$B$8)</f>
         <v/>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="56" t="str">
+      <c r="B11" s="50"/>
+      <c r="C11" s="49" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$9),"",Invulformulier!$B$9)</f>
         <v/>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="39" t="str">
+      <c r="D11" s="50"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="35" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$10),"",Invulformulier!$B$10)</f>
         <v/>
       </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
-    </row>
-    <row r="12" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="str">
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
+    </row>
+    <row r="12" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="25" t="str">
         <f>Invulformulier!A11</f>
         <v>System</v>
       </c>
-      <c r="B12" s="43"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="2"/>
       <c r="D12" s="14"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="26" t="str">
+      <c r="F12" s="25" t="str">
         <f>Invulformulier!A12</f>
         <v>Number of rounds</v>
       </c>
@@ -1282,25 +1197,25 @@
       <c r="I12" s="14"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="53" t="str">
+    <row r="13" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$11),"",Invulformulier!$B$11)</f>
         <v/>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="53" t="str">
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$12),"",Invulformulier!$B$12)</f>
         <v/>
       </c>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="55"/>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="str">
         <f>Invulformulier!A13</f>
         <v>Number of players</v>
@@ -1318,25 +1233,25 @@
       <c r="I14" s="14"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="62" t="str">
+    <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="58" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$13),"",Invulformulier!$B$13)</f>
         <v/>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="53" t="str">
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$14),"",Invulformulier!$B$14)</f>
         <v/>
       </c>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="55"/>
-    </row>
-    <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="48"/>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="str">
         <f>Invulformulier!A15</f>
         <v>Number of federations represented</v>
@@ -1354,25 +1269,25 @@
       <c r="I16" s="14"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62" t="str">
+    <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="58" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$15),"",Invulformulier!$B$15)</f>
         <v/>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="53" t="str">
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$16),"",Invulformulier!$B$16)</f>
         <v/>
       </c>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="55"/>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="48"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="str">
         <f>Invulformulier!A17</f>
         <v>Time control</v>
@@ -1387,303 +1302,253 @@
       <c r="I18" s="2"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="53" t="str">
+    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$17),"",Invulformulier!$B$17)</f>
         <v/>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="55"/>
-    </row>
-    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-    </row>
-    <row r="23" spans="1:10" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-    </row>
-    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="str">
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="48"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="20" t="str">
         <f>Invulformulier!A18</f>
         <v>Name</v>
       </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="29" t="str">
+        <f>Invulformulier!A19</f>
+        <v>Signature</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="43" t="str">
+        <f>IF(ISBLANK(Invulformulier!$B$18),"",Invulformulier!$B$18)</f>
+        <v/>
+      </c>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="45"/>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="29" t="str">
+        <f>Invulformulier!A20</f>
+        <v>Position</v>
+      </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="30" t="str">
-        <f>Invulformulier!A19</f>
-        <v>Signature</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="29" t="str">
+        <f>Invulformulier!A21</f>
+        <v>Federation</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="29" t="str">
+        <f>Invulformulier!A22</f>
+        <v>Date</v>
+      </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="15"/>
     </row>
-    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="59" t="str">
-        <f>IF(ISBLANK(Invulformulier!$B$18),"",Invulformulier!$B$18)</f>
-        <v/>
-      </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="61"/>
-    </row>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="str">
-        <f>Invulformulier!A20</f>
-        <v>Position</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="30" t="str">
-        <f>Invulformulier!A21</f>
-        <v>Federation</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="30" t="str">
-        <f>Invulformulier!A22</f>
-        <v>Date</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="47" t="str">
+    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="52" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$20),"",Invulformulier!$B$20)</f>
         <v/>
       </c>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="47" t="str">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="52" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$21),"",Invulformulier!$B$21)</f>
         <v>BEL</v>
       </c>
-      <c r="F28" s="49"/>
-      <c r="G28" s="47" t="str">
+      <c r="F26" s="54"/>
+      <c r="G26" s="52" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$22),"",Invulformulier!$B$22)</f>
         <v/>
       </c>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="49"/>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="str">
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="54"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="29" t="str">
         <f>Invulformulier!A23</f>
         <v>Name of the Authenticating Federation official</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="30" t="str">
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="29" t="str">
         <f>Invulformulier!A24</f>
         <v>Position of the Authenticating Federation official</v>
       </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="33"/>
-    </row>
-    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="59" t="str">
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="32"/>
+    </row>
+    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="43" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$23),"",Invulformulier!$B$23)</f>
-        <v>IA/IO/FT CORNET, Luc (205494)</v>
-      </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="59" t="str">
+        <v>IA CORNET, Luc (205494)</v>
+      </c>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="43" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$24),"",Invulformulier!$B$24)</f>
         <v>Belgian FIDE Delegate</v>
       </c>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="61"/>
-    </row>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="str">
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="45"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="20" t="str">
         <f>Invulformulier!A25</f>
         <v>Signature</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="30" t="str">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="29" t="str">
         <f>Invulformulier!A26</f>
         <v>Date</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="47" t="str">
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="15"/>
+    </row>
+    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="55"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="52" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$26),"",Invulformulier!$B$26)</f>
         <v/>
       </c>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="49"/>
-    </row>
-    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="38" t="s">
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="54"/>
+    </row>
+    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-    </row>
-    <row r="35" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="38" t="s">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+    </row>
+    <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+      <c r="A37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="24"/>
+    </row>
+    <row r="38" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-    </row>
-    <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-    </row>
-    <row r="37" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-    </row>
-    <row r="39" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="17"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A40" s="42" t="s">
         <v>39</v>
-      </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="25"/>
-    </row>
-    <row r="40" spans="1:10" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="18"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="46" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E30:J30"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:J28"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="F5:J5"/>
     <mergeCell ref="A7:E7"/>
@@ -1691,22 +1556,6 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="C11:E11"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
